--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488042_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488042_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5943</v>
+        <v>7.3793</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2676</v>
+        <v>3.7999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3267</v>
+        <v>3.5794</v>
       </c>
       <c r="G2" t="n">
         <v>4.4017</v>
@@ -610,13 +610,13 @@
         <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1685</v>
+        <v>0.9535</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1613</v>
+        <v>0.3709</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3298</v>
+        <v>0.5825</v>
       </c>
       <c r="V2" t="n">
         <v>1.0331</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6743</v>
+        <v>3.6006</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.2987</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6466</v>
+        <v>3.8993</v>
       </c>
       <c r="G3" t="n">
         <v>2.7959</v>
@@ -688,13 +688,13 @@
         <v>1.1893</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1656</v>
+        <v>0.7607</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4147</v>
+        <v>0.2589</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2491</v>
+        <v>0.5019</v>
       </c>
       <c r="V3" t="n">
         <v>0.8369</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5052</v>
+        <v>1.6091</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2126</v>
+        <v>0.5411</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2926</v>
+        <v>1.068</v>
       </c>
       <c r="G4" t="n">
         <v>2.6836</v>
@@ -766,13 +766,13 @@
         <v>2.3787</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1203</v>
+        <v>1.2242</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.242</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3623</v>
+        <v>1.1376</v>
       </c>
       <c r="V4" t="n">
         <v>-1.704</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. ESCOLANO ZAVALA</t>
+          <t>D. GUAITA MACHADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0284</v>
+        <v>0.4215</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1881</v>
+        <v>-1.7293</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2165</v>
+        <v>2.1507</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1663</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8716</v>
+        <v>0.5698</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2947</v>
+        <v>-1.3295</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.803</v>
+        <v>-0.3361</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8873</v>
+        <v>0.4843</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0842</v>
+        <v>-0.8204</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3633</v>
+        <v>-0.4235</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0157</v>
+        <v>0.0856</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.379</v>
+        <v>-0.5091</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9911</v>
+        <v>0.3964</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9822</v>
+        <v>2.3787</v>
       </c>
       <c r="S5" t="n">
-        <v>2.382</v>
+        <v>0.167</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3217</v>
+        <v>-0.0145</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0603</v>
+        <v>0.1815</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1962</v>
+        <v>0.6176</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2666</v>
+        <v>0.6036</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4627</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GUAITA MACHADO</t>
+          <t>F. MONTIEL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5121</v>
+        <v>-0.2379</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.6066</v>
+        <v>-1.557</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0946</v>
+        <v>1.3191</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.1384</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5698</v>
+        <v>-1.7224</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3295</v>
+        <v>1.584</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3361</v>
+        <v>1.1154</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4843</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8204</v>
+        <v>1.9687</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4235</v>
+        <v>-1.2538</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0856</v>
+        <v>-0.8691</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5091</v>
+        <v>-0.3847</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3964</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3787</v>
+        <v>1.784</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7665</v>
+        <v>-0.2523</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8918</v>
+        <v>-0.3532</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1253</v>
+        <v>0.1008</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6176</v>
+        <v>0.3511</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6036</v>
+        <v>-0.337</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0141</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6627</v>
+        <v>-0.459</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4243</v>
+        <v>-0.2205</v>
       </c>
       <c r="F7" t="n">
         <v>-0.2384</v>
@@ -1000,10 +1000,10 @@
         <v>0.9911</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4809</v>
+        <v>-0.2772</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4257</v>
+        <v>-0.222</v>
       </c>
       <c r="U7" t="n">
         <v>-0.0552</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. MONTIEL RODRIGUEZ</t>
+          <t>N. ESCOLANO ZAVALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8034</v>
+        <v>-0.4861</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0663</v>
+        <v>-2.6745</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2629</v>
+        <v>2.1884</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1384</v>
+        <v>-1.1663</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7224</v>
+        <v>-0.8716</v>
       </c>
       <c r="I8" t="n">
-        <v>1.584</v>
+        <v>-0.2947</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1154</v>
+        <v>-0.803</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8532999999999999</v>
+        <v>-0.8873</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9687</v>
+        <v>0.0842</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2538</v>
+        <v>-0.3633</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8691</v>
+        <v>0.0157</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3847</v>
+        <v>-0.379</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R8" t="n">
-        <v>1.784</v>
+        <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8179</v>
+        <v>1.8675</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8625</v>
+        <v>0.8353</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0447</v>
+        <v>1.0322</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3511</v>
+        <v>-0.1962</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.337</v>
+        <v>0.2666</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6879999999999999</v>
+        <v>-0.4627</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>A. KRASTS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8821</v>
+        <v>-1.7959</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0066</v>
+        <v>-3.6687</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1246</v>
+        <v>1.8729</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0046</v>
+        <v>-2.3532</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6703</v>
+        <v>-1.9877</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6656</v>
+        <v>-0.3655</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7825</v>
+        <v>-1.8427</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.0236</v>
+        <v>-1.3243</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2411</v>
+        <v>-0.5184</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7779</v>
+        <v>-0.5105</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3533</v>
+        <v>-0.6634</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4246</v>
+        <v>0.1529</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.784</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9645</v>
+        <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1805</v>
+        <v>1.5858</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2032</v>
+        <v>0.7204</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9406</v>
+        <v>0.1562</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2626</v>
+        <v>0.5642</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2966</v>
+        <v>0.2334</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0964</v>
+        <v>0.2334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. KRASTS</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5703</v>
+        <v>-2.8675</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5274</v>
+        <v>-3.8798</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9571</v>
+        <v>1.0123</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3532</v>
+        <v>-1.0046</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9877</v>
+        <v>-1.6703</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3655</v>
+        <v>0.6656</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8427</v>
+        <v>-1.7825</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3243</v>
+        <v>-2.0236</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5184</v>
+        <v>0.2411</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5105</v>
+        <v>0.7779</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6634</v>
+        <v>0.3533</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1529</v>
+        <v>0.4246</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3964</v>
+        <v>-1.784</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9822</v>
+        <v>-3.9645</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S10" t="n">
-        <v>0.946</v>
+        <v>1.2178</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2975</v>
+        <v>1.0675</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6485</v>
+        <v>0.1503</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2334</v>
+        <v>-1.2966</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2334</v>
+        <v>-2.0964</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1733</v>
+        <v>-5.3417</v>
       </c>
       <c r="E11" t="n">
         <v>-4.2711</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9022</v>
+        <v>-1.0707</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7672</v>
@@ -1312,13 +1312,13 @@
         <v>0.3964</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.1781</v>
       </c>
       <c r="T11" t="n">
         <v>-0.312</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3024</v>
+        <v>0.1339</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8107</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.198299999999999</v>
+        <v>1.822400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.5825</v>
+        <v>-13.9586</v>
       </c>
       <c r="F12" t="n">
         <v>15.781</v>
@@ -1363,7 +1363,7 @@
         <v>9.422299999999998</v>
       </c>
       <c r="J12" t="n">
-        <v>2.632699999999999</v>
+        <v>2.6327</v>
       </c>
       <c r="K12" t="n">
         <v>-3.2231</v>
@@ -1390,13 +1390,13 @@
         <v>16.8489</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5795</v>
+        <v>6.203500000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2498</v>
+        <v>1.8736</v>
       </c>
       <c r="U12" t="n">
-        <v>4.329800000000001</v>
+        <v>4.3297</v>
       </c>
       <c r="V12" t="n">
         <v>-3.395</v>
@@ -1405,7 +1405,7 @@
         <v>3.3397</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.734800000000001</v>
+        <v>-6.7348</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.477600000000001</v>
+        <v>9.1602</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2216</v>
+        <v>5.3048</v>
       </c>
       <c r="F13" t="n">
-        <v>3.256</v>
+        <v>3.8555</v>
       </c>
       <c r="G13" t="n">
         <v>4.3467</v>
@@ -1468,13 +1468,13 @@
         <v>3.7662</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1329</v>
+        <v>-0.1844</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6464</v>
+        <v>-0.2704</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5134</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>3.2139</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7954</v>
+        <v>2.3635</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3151</v>
+        <v>0.6207</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4802</v>
+        <v>1.7427</v>
       </c>
       <c r="G14" t="n">
         <v>3.0588</v>
@@ -1546,13 +1546,13 @@
         <v>2.3787</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.191</v>
+        <v>0.3771</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5798</v>
+        <v>-0.2742</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3889</v>
+        <v>0.6514</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4778</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.649</v>
+        <v>0.8495</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.7925</v>
+        <v>-2.6907</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4416</v>
+        <v>3.5402</v>
       </c>
       <c r="G15" t="n">
         <v>1.3629</v>
@@ -1624,13 +1624,13 @@
         <v>2.9733</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.3726</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9835</v>
+        <v>-0.8817</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4105</v>
+        <v>0.5091</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1408</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4897</v>
+        <v>0.506</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1629</v>
+        <v>-0.3666</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6526</v>
+        <v>0.8726</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6591</v>
@@ -1702,13 +1702,13 @@
         <v>2.5769</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7036</v>
+        <v>-0.6873</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.422</v>
+        <v>-0.6257</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2817</v>
+        <v>-0.0616</v>
       </c>
       <c r="V16" t="n">
         <v>0.2666</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. CABARROCAS MARTIN</t>
+          <t>J. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0757</v>
+        <v>-0.6957</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8113</v>
+        <v>-2.425</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8869</v>
+        <v>1.7293</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3368</v>
+        <v>-2.2151</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4611</v>
+        <v>-0.7496</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-1.4656</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9887</v>
+        <v>-1.1767</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9887</v>
+        <v>-0.4975</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.6791</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3255</v>
+        <v>-1.0385</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5276</v>
+        <v>-0.252</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.7864</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9911</v>
+        <v>2.5769</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2611</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5471</v>
+        <v>-0.5238</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.286</v>
+        <v>-0.1461</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="W17" t="n">
         <v>0.2666</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2666</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MARTIN GONZALEZ</t>
+          <t>R. CABARROCAS MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4534</v>
+        <v>-0.7607</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3232</v>
+        <v>0.0982</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8697</v>
+        <v>-0.8589</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2151</v>
+        <v>-0.3368</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7496</v>
+        <v>0.4611</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4656</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1767</v>
+        <v>0.9887</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4975</v>
+        <v>0.9887</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6791</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0385</v>
+        <v>-1.3255</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.252</v>
+        <v>-0.5276</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7864</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5769</v>
+        <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4276</v>
+        <v>-0.4239</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.422</v>
+        <v>-0.166</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0057</v>
+        <v>-0.2579</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0.2666</v>
       </c>
       <c r="X18" t="n">
-        <v>0.337</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="19">
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6224</v>
+        <v>-1.5206</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4207</v>
+        <v>-1.3188</v>
       </c>
       <c r="F19" t="n">
         <v>-0.2018</v>
@@ -1936,10 +1936,10 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. LOPEZ SANCHEZ</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2895</v>
+        <v>-2.1515</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9063</v>
+        <v>-5.6452</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3833</v>
+        <v>3.4937</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6755</v>
+        <v>-3.8644</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1343</v>
+        <v>-2.753</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8098</v>
+        <v>-1.1115</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.612</v>
+        <v>-4.652</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6659</v>
+        <v>-3.3818</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2779</v>
+        <v>-1.2701</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0634</v>
+        <v>0.7875</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5315</v>
+        <v>0.6289</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5319</v>
+        <v>0.1586</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1893</v>
+        <v>1.784</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7929</v>
+        <v>2.7751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7617</v>
+        <v>-0.3377</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.312</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4497</v>
+        <v>0.4642</v>
       </c>
       <c r="V20" t="n">
-        <v>0.337</v>
+        <v>0.2666</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="X20" t="n">
-        <v>0.337</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>J. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4745</v>
+        <v>-3.0473</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.2564</v>
+        <v>-2.8044</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7819</v>
+        <v>-0.2429</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.8644</v>
+        <v>-1.6755</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.753</v>
+        <v>0.1343</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1115</v>
+        <v>-1.8098</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.652</v>
+        <v>-0.612</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.3818</v>
+        <v>0.6659</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2701</v>
+        <v>-1.2779</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7875</v>
+        <v>-1.0634</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6289</v>
+        <v>-0.5315</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1586</v>
+        <v>-0.5319</v>
       </c>
       <c r="P21" t="n">
-        <v>1.784</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7751</v>
+        <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6607</v>
+        <v>-0.5194</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4131</v>
+        <v>-0.2101</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2476</v>
+        <v>-0.3093</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2666</v>
+        <v>0.337</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5331</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6946</v>
+        <v>-3.1855</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.5931</v>
+        <v>-5.88</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8985</v>
+        <v>2.6945</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4272</v>
@@ -2170,13 +2170,13 @@
         <v>2.9733</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5935</v>
+        <v>-0.0844</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3286</v>
+        <v>-0.6155</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2649</v>
+        <v>0.5312</v>
       </c>
       <c r="V22" t="n">
         <v>-0.674</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.198399999999999</v>
+        <v>1.517900000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-15.1071</v>
+        <v>-15.107</v>
       </c>
       <c r="F23" t="n">
-        <v>13.9085</v>
+        <v>16.6249</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.9697</v>
+        <v>-3.969700000000001</v>
       </c>
       <c r="H23" t="n">
         <v>5.4526</v>
@@ -2221,7 +2221,7 @@
         <v>-9.4224</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.337000000000002</v>
+        <v>-1.337000000000001</v>
       </c>
       <c r="K23" t="n">
         <v>2.229899999999999</v>
@@ -2248,19 +2248,19 @@
         <v>21.8044</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.5796</v>
+        <v>-2.863</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.3299</v>
+        <v>-4.329800000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2496</v>
+        <v>1.467</v>
       </c>
       <c r="V23" t="n">
         <v>3.395100000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>7.4086</v>
+        <v>7.408600000000001</v>
       </c>
       <c r="X23" t="n">
         <v>-4.0137</v>
